--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4.32</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>4.74</v>
       </c>
       <c r="P26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.56</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>4.74</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.32</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
-        <v>2.46</v>
+        <v>4.74</v>
       </c>
       <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.56</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46055.22916666666</v>
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46055.375</v>
@@ -1144,25 +1144,25 @@
         <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1171,37 +1171,37 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46055.39583333334</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46055.51041666666</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46055.58333333334</v>
+        <v>46055.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46055.60416666666</v>
+        <v>46055.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2453,64 +2453,64 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>4.48</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46055.625</v>
+        <v>46055.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.12</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46055.625</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46055.65625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.32</v>
+        <v>4.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="O25" t="n">
-        <v>4.74</v>
+        <v>4.02</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3518,70 +3518,70 @@
         <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.56</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AG26" t="n">
         <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46055.69791666666</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46055.73958333334</v>
@@ -4426,27 +4426,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,76 +4467,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46055.79166666666</v>
+        <v>46055.75</v>
       </c>
     </row>
     <row r="35">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46055.83333333334</v>
+        <v>46055.85416666666</v>
       </c>
     </row>
     <row r="36">

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O17" t="n">
-        <v>4.78</v>
+        <v>2.37</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>4.31</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.37</v>
+        <v>4.78</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.31</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.89</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2682,46 +2682,46 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
         <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
         <v>3.08</v>
@@ -2730,19 +2730,19 @@
         <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
         <v>1.28</v>
@@ -2831,7 +2831,7 @@
         <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
@@ -2843,13 +2843,13 @@
         <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
         <v>2.89</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.68</v>
+        <v>2.58</v>
       </c>
       <c r="O23" t="n">
-        <v>4.42</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE23" t="n">
         <v>1.46</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.1</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.15</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V27" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.81</v>
-      </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>3.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U29" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O30" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.49</v>
@@ -4054,7 +4054,7 @@
         <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
         <v>1.25</v>
@@ -4125,7 +4125,7 @@
         <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.43</v>
@@ -4149,16 +4149,16 @@
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AA31" t="n">
         <v>2.26</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
@@ -4229,16 +4229,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="M32" t="n">
         <v>3.11</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="P32" t="n">
         <v>2.05</v>
@@ -4256,7 +4256,7 @@
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
         <v>7</v>
@@ -4274,7 +4274,7 @@
         <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
         <v>1.66</v>
@@ -4295,7 +4295,7 @@
         <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4354,7 +4354,7 @@
         <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="O33" t="n">
         <v>9</v>
@@ -4363,7 +4363,7 @@
         <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
@@ -4372,13 +4372,13 @@
         <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U33" t="n">
         <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.08</v>
@@ -4405,10 +4405,10 @@
         <v>1.34</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG33" t="n">
         <v>3.6</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
         <v>2.4</v>
@@ -4503,19 +4503,19 @@
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>3.78</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1614,16 +1614,16 @@
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
         <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.49</v>
@@ -1632,52 +1632,52 @@
         <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
         <v>3.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46055.51041666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.37</v>
+        <v>3.93</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.31</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.89</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>4.78</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>4.29</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.91</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.95</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>1.82</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,49 +3277,49 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="N24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.68</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.71</v>
-      </c>
       <c r="V24" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA24" t="n">
         <v>1.47</v>
@@ -3328,22 +3328,22 @@
         <v>2.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,49 +3396,49 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="O25" t="n">
-        <v>4.02</v>
+        <v>4.42</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V25" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA25" t="n">
         <v>1.47</v>
@@ -3447,22 +3447,22 @@
         <v>2.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.81</v>
-      </c>
       <c r="Q27" t="n">
-        <v>4.12</v>
+        <v>3.08</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T29" t="n">
         <v>3.1</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.15</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>4.45</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.56</v>
+        <v>3.11</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O31" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
         <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
         <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.11</v>
+        <v>3.56</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
         <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.06</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
         <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1983,19 +1983,19 @@
         <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
         <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
         <v>7.9</v>
@@ -2007,25 +2007,25 @@
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
         <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.09</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
         <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
         <v>1.81</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.91</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.45</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.07</v>
+        <v>5.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>7.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>4.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>6.07</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
       <c r="AB15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.23</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>1.19</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="M19" t="n">
         <v>3.2</v>
@@ -2691,7 +2691,7 @@
         <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="P19" t="n">
         <v>1.99</v>
@@ -2709,13 +2709,13 @@
         <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
@@ -2724,13 +2724,13 @@
         <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
         <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
         <v>3.65</v>
@@ -2739,13 +2739,13 @@
         <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
         <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
         <v>1.3</v>
@@ -2804,10 +2804,10 @@
         <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
         <v>8.08</v>
@@ -2825,16 +2825,16 @@
         <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>6.55</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
@@ -2843,7 +2843,7 @@
         <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="AA20" t="n">
         <v>1.85</v>
@@ -2855,16 +2855,16 @@
         <v>2.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
         <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
         <v>1.06</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.68</v>
+        <v>2.58</v>
       </c>
       <c r="O25" t="n">
-        <v>4.42</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE25" t="n">
         <v>1.46</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>1.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>4.02</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
         <v>2.25</v>
@@ -3649,13 +3649,13 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
         <v>3.15</v>
@@ -3667,13 +3667,13 @@
         <v>8.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
         <v>2.89</v>
@@ -3685,10 +3685,10 @@
         <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
         <v>1.83</v>
@@ -3700,7 +3700,7 @@
         <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="M29" t="n">
         <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
@@ -4000,28 +4000,28 @@
         <v>1.95</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
         <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
         <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
         <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
         <v>1.04</v>
@@ -4030,19 +4030,19 @@
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
         <v>3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
         <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AD30" t="n">
         <v>1.22</v>
@@ -4051,13 +4051,13 @@
         <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46055.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.11</v>
+        <v>3.56</v>
       </c>
       <c r="N31" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
         <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
         <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.06</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>3.11</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O32" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
         <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
         <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4354,34 +4354,34 @@
         <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
         <v>9</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="T33" t="n">
         <v>2.71</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
@@ -4393,7 +4393,7 @@
         <v>3.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB33" t="n">
         <v>2</v>
@@ -4405,13 +4405,13 @@
         <v>1.34</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
         <v>1.02</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="O34" t="n">
         <v>2.4</v>
@@ -4491,10 +4491,10 @@
         <v>2.65</v>
       </c>
       <c r="T34" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
         <v>8</v>
@@ -4530,7 +4530,7 @@
         <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
         <v>1.91</v>
@@ -4589,7 +4589,7 @@
         <v>1.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
         <v>3.4</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -659,43 +659,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
         <v>4.88</v>
       </c>
       <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.35</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
@@ -707,7 +707,7 @@
         <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
@@ -716,16 +716,16 @@
         <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
         <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46055.22916666666</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
         <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
         <v>4.65</v>
@@ -1037,7 +1037,7 @@
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
         <v>2.71</v>
@@ -1046,7 +1046,7 @@
         <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
@@ -1058,13 +1058,13 @@
         <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
         <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>3.05</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="M6" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>3.54</v>
@@ -1165,10 +1165,10 @@
         <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.11</v>
@@ -1195,7 +1195,7 @@
         <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
         <v>1.36</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="O10" t="n">
         <v>7.85</v>
@@ -1638,7 +1638,7 @@
         <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V10" t="n">
         <v>3.75</v>
@@ -1659,13 +1659,13 @@
         <v>1.34</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="n">
         <v>1.76</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
         <v>3.45</v>
@@ -1992,10 +1992,10 @@
         <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
         <v>7.9</v>
@@ -2025,16 +2025,16 @@
         <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46055.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.23</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2206,22 +2206,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>7.5</v>
+        <v>7.94</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>13.13</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.91</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
@@ -2233,7 +2233,7 @@
         <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
         <v>3.8</v>
@@ -2254,25 +2254,25 @@
         <v>1.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>5.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M16" t="n">
         <v>4.8</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.6</v>
-      </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>7.29</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>2.17</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.99</v>
+        <v>5.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>3.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2566,7 +2566,7 @@
         <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
         <v>3.75</v>
@@ -2587,16 +2587,16 @@
         <v>2.97</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
         <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
@@ -2605,7 +2605,7 @@
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
         <v>1.49</v>
@@ -2626,7 +2626,7 @@
         <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
         <v>1.83</v>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="P19" t="n">
         <v>1.99</v>
@@ -2709,7 +2709,7 @@
         <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
         <v>7.9</v>
@@ -2724,13 +2724,13 @@
         <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
         <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
         <v>3.65</v>
@@ -2742,10 +2742,10 @@
         <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
         <v>1.3</v>
@@ -2804,7 +2804,7 @@
         <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="N20" t="n">
         <v>1.38</v>
@@ -2825,7 +2825,7 @@
         <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
         <v>1.42</v>
@@ -2840,7 +2840,7 @@
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
         <v>3.62</v>
@@ -2864,7 +2864,7 @@
         <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
         <v>1.06</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="M21" t="n">
         <v>3.9</v>
@@ -2932,7 +2932,7 @@
         <v>3.91</v>
       </c>
       <c r="P21" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
         <v>2.2</v>
@@ -2947,40 +2947,40 @@
         <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
         <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA21" t="n">
         <v>1.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AC21" t="n">
         <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
         <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
         <v>1.19</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>3.79</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>4.11</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>2.29</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.12</v>
+        <v>2.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>4.42</v>
+        <v>2.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.09</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>4.35</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="R25" t="n">
         <v>1.22</v>
@@ -3420,13 +3420,13 @@
         <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W25" t="n">
         <v>1.13</v>
@@ -3435,34 +3435,34 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.02</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.55</v>
-      </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="V27" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.1</v>
+        <v>3.02</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.85</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O30" t="n">
         <v>4.2</v>
@@ -4018,7 +4018,7 @@
         <v>3.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
         <v>8.5</v>
@@ -4030,7 +4030,7 @@
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
         <v>3</v>
@@ -4039,7 +4039,7 @@
         <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC30" t="n">
         <v>3.86</v>
@@ -4054,10 +4054,10 @@
         <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46055.69791666666</v>
@@ -4113,10 +4113,10 @@
         <v>1.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>2.35</v>
@@ -4128,7 +4128,7 @@
         <v>5.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
         <v>2.6</v>
@@ -4158,7 +4158,7 @@
         <v>2.26</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
@@ -4167,16 +4167,16 @@
         <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
         <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="M32" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
         <v>3.03</v>
@@ -4247,10 +4247,10 @@
         <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -4259,10 +4259,10 @@
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
         <v>1.08</v>
@@ -4271,7 +4271,7 @@
         <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA32" t="n">
         <v>2.2</v>
@@ -4283,7 +4283,7 @@
         <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
         <v>1.85</v>
@@ -4354,34 +4354,34 @@
         <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O33" t="n">
         <v>9</v>
       </c>
       <c r="P33" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
         <v>6.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
@@ -4390,10 +4390,10 @@
         <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB33" t="n">
         <v>2</v>
@@ -4402,19 +4402,19 @@
         <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46055.73958333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>2.41</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
         <v>4.88</v>
@@ -692,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
@@ -707,7 +707,7 @@
         <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
@@ -716,16 +716,16 @@
         <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46055.22916666666</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.12</v>
@@ -1034,55 +1034,55 @@
         <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="AA5" t="n">
         <v>1.87</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>1.82</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46055.375</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M14" t="n">
         <v>4.6</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>7.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.27</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>2.89</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>7.94</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>13.13</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.18</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.300000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>7.94</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>13.13</v>
       </c>
       <c r="O16" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>3.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.29</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>3.42</v>
+        <v>4.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.05</v>
+        <v>6.07</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.05</v>
+        <v>5.58</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.93</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
         <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>4.29</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.28</v>
+        <v>5.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>3.93</v>
       </c>
       <c r="P18" t="n">
         <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.29</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.6</v>
+        <v>3.28</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.64</v>
+        <v>2.02</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.91</v>
+        <v>2.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.53</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>4.11</v>
+        <v>4.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.3</v>
+        <v>5.85</v>
       </c>
       <c r="AA22" t="n">
         <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>3.64</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>1.76</v>
       </c>
       <c r="O23" t="n">
-        <v>2.55</v>
+        <v>3.91</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>3.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.02</v>
+        <v>4.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2090,10 +2090,10 @@
         <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5</v>
+        <v>7.35</v>
       </c>
       <c r="O14" t="n">
         <v>1.79</v>
@@ -2111,10 +2111,10 @@
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
         <v>4.6</v>
@@ -2126,13 +2126,13 @@
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB14" t="n">
         <v>2.32</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>7.94</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>13.13</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>3.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>2.86</v>
+        <v>4.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.27</v>
+        <v>6.07</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.06</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>5.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>7.94</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>13.13</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.300000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>4.45</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.8</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
         <v>3.8</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.58</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.55</v>
+        <v>4.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>2.09</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>5.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AC28" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3994,10 +3994,10 @@
         <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O30" t="n">
         <v>4.2</v>
@@ -4009,10 +4009,10 @@
         <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
         <v>3.25</v>
@@ -4024,13 +4024,13 @@
         <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
         <v>3</v>
@@ -4039,7 +4039,7 @@
         <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>3.86</v>
@@ -4048,16 +4048,16 @@
         <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AF30" t="n">
         <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46055.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.72</v>
+        <v>2.51</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>3.03</v>
       </c>
       <c r="O31" t="n">
-        <v>2.35</v>
+        <v>2.84</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="T31" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
         <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W31" t="n">
         <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.51</v>
+        <v>1.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.84</v>
+        <v>2.35</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>2.14</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -662,10 +662,10 @@
         <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>2.41</v>
@@ -689,7 +689,7 @@
         <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -707,7 +707,7 @@
         <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
@@ -719,13 +719,13 @@
         <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46055.22916666666</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>2.21</v>
@@ -1034,10 +1034,10 @@
         <v>4.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
         <v>2.79</v>
@@ -1058,31 +1058,31 @@
         <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AC5" t="n">
         <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
         <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46055.375</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.68</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.78</v>
-      </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>3.54</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
         <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1986,16 +1986,16 @@
         <v>3.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
         <v>7.9</v>
@@ -2007,34 +2007,34 @@
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
         <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46055.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>7.94</v>
+        <v>4.95</v>
       </c>
       <c r="N15" t="n">
-        <v>13.13</v>
+        <v>7.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="P15" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
         <v>4.45</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.07</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.58</v>
+        <v>2.89</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>3.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>6.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.94</v>
+        <v>4.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
         <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
         <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46055.625</v>
@@ -2804,7 +2804,7 @@
         <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
         <v>1.38</v>
@@ -2816,7 +2816,7 @@
         <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
@@ -2840,7 +2840,7 @@
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
         <v>3.62</v>
@@ -2849,10 +2849,10 @@
         <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="AD20" t="n">
         <v>1.32</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4.27</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
         <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.85</v>
+        <v>5.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.55</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>2.09</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>5.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>3.64</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>4.65</v>
+        <v>3.84</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3438,31 +3438,31 @@
         <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.79</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>4.11</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.29</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.59</v>
+        <v>2.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
         <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.02</v>
+        <v>2.71</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
         <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R27" t="n">
         <v>1.45</v>
@@ -3658,10 +3658,10 @@
         <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
         <v>8.4</v>
@@ -3670,7 +3670,7 @@
         <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
         <v>1.38</v>
@@ -3682,13 +3682,13 @@
         <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
         <v>1.83</v>
@@ -3700,7 +3700,7 @@
         <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4110,16 +4110,16 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="P31" t="n">
         <v>2.05</v>
@@ -4131,13 +4131,13 @@
         <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
         <v>9.300000000000001</v>
@@ -4170,7 +4170,7 @@
         <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
         <v>1.36</v>
@@ -4232,28 +4232,28 @@
         <v>1.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="O32" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.75</v>
+        <v>5.68</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
         <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
@@ -4262,7 +4262,7 @@
         <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
@@ -4271,31 +4271,31 @@
         <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
         <v>2.26</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD32" t="n">
         <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AF32" t="n">
         <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4360,10 +4360,10 @@
         <v>9</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
@@ -4372,7 +4372,7 @@
         <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U33" t="n">
         <v>1.44</v>
@@ -4390,10 +4390,10 @@
         <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
         <v>2</v>
@@ -4402,19 +4402,19 @@
         <v>3.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.11</v>
+        <v>3.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46055.73958333334</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
         <v>2.4</v>
@@ -4485,16 +4485,16 @@
         <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T34" t="n">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
         <v>8</v>
@@ -4521,7 +4521,7 @@
         <v>3.78</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
         <v>1.85</v>
@@ -4530,10 +4530,10 @@
         <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46055.75</v>
@@ -4589,7 +4589,7 @@
         <v>1.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
         <v>3.4</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46055.44444444445</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46055.48263888889</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="O10" t="n">
-        <v>7.85</v>
+        <v>7.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.4</v>
+        <v>6.11</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
         <v>1.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46055.51041666666</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46055.54166666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>7.35</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>7.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.94</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>2.89</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>4.95</v>
+        <v>7.75</v>
       </c>
       <c r="N15" t="n">
-        <v>7.35</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>3.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.32</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.45</v>
+        <v>6.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.89</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>4.72</v>
       </c>
       <c r="M16" t="n">
-        <v>7.75</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.699999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.8</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
         <v>3.8</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
         <v>1.93</v>
@@ -2388,10 +2388,10 @@
         <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>4.78</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.29</v>
+        <v>2.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.93</v>
+        <v>2.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.28</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>4.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
         <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.79</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="O22" t="n">
-        <v>4.11</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.29</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
         <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
         <v>1.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>3.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.85</v>
+        <v>7.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="AG24" t="n">
         <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.64</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.91</v>
+        <v>2.55</v>
       </c>
       <c r="P25" t="n">
-        <v>2.53</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>2.57</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>3.84</v>
+        <v>5.85</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.8</v>
+        <v>3.86</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>3.79</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>4.11</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>2.21</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z26" t="n">
         <v>5.5</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AA26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>2.71</v>
       </c>
       <c r="M29" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.24</v>
+        <v>5.54</v>
       </c>
       <c r="M7" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
         <v>1.45</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46055.41666666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
         <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46055.52083333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.72</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>7.35</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>7.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.94</v>
+        <v>4.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>2.89</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>2.12</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.42</v>
+        <v>2.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="U21" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>5.85</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>3.86</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.71</v>
+        <v>2.24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>3.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="N24" t="n">
-        <v>1.76</v>
+        <v>5.02</v>
       </c>
       <c r="O24" t="n">
-        <v>3.91</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>3.82</v>
+        <v>6.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.81</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>2.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.12</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.57</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>5.85</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.86</v>
+        <v>5.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.79</v>
+        <v>4.25</v>
       </c>
       <c r="M26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.68</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.15</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.46</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O31" t="n">
         <v>2.5</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.25</v>
       </c>
-      <c r="N32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.68</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T3" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>7.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.94</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="n">
         <v>1.93</v>
@@ -2150,10 +2150,10 @@
         <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>7.75</v>
+        <v>4.95</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="P15" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.699999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M16" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>5.02</v>
       </c>
       <c r="O21" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="T21" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>5.85</v>
+        <v>6.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.91</v>
+        <v>2.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.53</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>3.82</v>
+        <v>5.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.79</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>3.91</v>
       </c>
       <c r="P23" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.2</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>5.02</v>
+        <v>2.64</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.79</v>
+        <v>3.82</v>
       </c>
       <c r="T24" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>2.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>3.79</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.82</v>
+        <v>2.21</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
         <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
         <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>4.15</v>
       </c>
       <c r="M27" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N27" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="O28" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>4.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>2.71</v>
       </c>
       <c r="M29" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.25</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.68</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O32" t="n">
         <v>2.5</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V32" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>7.75</v>
+        <v>4.95</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.699999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M15" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>7.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.94</v>
+        <v>6.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="n">
         <v>1.93</v>
@@ -2388,10 +2388,10 @@
         <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>2.55</v>
+        <v>3.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
-        <v>5.85</v>
+        <v>3.82</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.86</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>3.79</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>3.91</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.79</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.7</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AB25" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.15</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.46</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,61 +2206,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>7.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.94</v>
+        <v>6.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="n">
         <v>1.93</v>
@@ -2269,10 +2269,10 @@
         <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>7.75</v>
+        <v>4.95</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.699999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="V16" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.32</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.78</v>
+        <v>2.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="O18" t="n">
-        <v>2.24</v>
+        <v>4.78</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>3.79</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>5.02</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>4.11</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.9</v>
+        <v>2.21</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.79</v>
+        <v>3.68</v>
       </c>
       <c r="T21" t="n">
-        <v>2.67</v>
+        <v>2.09</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="W21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.09</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.28</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>5.02</v>
       </c>
       <c r="O22" t="n">
-        <v>3.91</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>3.82</v>
+        <v>6.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.81</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>2.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.79</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.68</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>3.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.35</v>
+        <v>7.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.12</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.57</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>5.85</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.86</v>
+        <v>5.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4.42</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>4.6</v>
+        <v>5.85</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>3.86</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.71</v>
+        <v>2.24</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M27" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>3.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="O28" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>4.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -4714,40 +4714,40 @@
         <v>4.06</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA36" t="n">
         <v>1.98</v>
@@ -4756,22 +4756,22 @@
         <v>1.83</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46055.89583333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>6.85</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46055.22916666666</v>
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T3" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>7.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.94</v>
+        <v>6.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="n">
         <v>1.93</v>
@@ -2150,10 +2150,10 @@
         <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,61 +2206,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>4.72</v>
       </c>
       <c r="M15" t="n">
-        <v>7.75</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.699999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AC15" t="n">
         <v>3.8</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
         <v>1.93</v>
@@ -2269,10 +2269,10 @@
         <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.79</v>
+        <v>2.12</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="N22" t="n">
-        <v>5.02</v>
+        <v>1.68</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>4.42</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>2.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="V22" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.81</v>
+        <v>2.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>1.55</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>1.68</v>
+        <v>5.02</v>
       </c>
       <c r="O23" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>2.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>3.79</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>4.11</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="T26" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
-        <v>5.85</v>
+        <v>4.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.86</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>2.71</v>
       </c>
       <c r="M29" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O31" t="n">
         <v>2.5</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V31" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
         <v>3.25</v>
       </c>
-      <c r="N32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.68</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>7.75</v>
+        <v>4.95</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>7.35</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="P14" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.699999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>4.95</v>
+        <v>7.75</v>
       </c>
       <c r="N16" t="n">
-        <v>7.35</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>3.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.32</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.45</v>
+        <v>6.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.89</v>
+        <v>5.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>2.24</v>
+        <v>4.78</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.32</v>
+        <v>1.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.78</v>
+        <v>2.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.55</v>
+        <v>3.79</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>5.02</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>2.21</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>2.79</v>
+        <v>3.68</v>
       </c>
       <c r="T23" t="n">
-        <v>2.67</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V23" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="W23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.09</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.28</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="N24" t="n">
-        <v>1.76</v>
+        <v>5.02</v>
       </c>
       <c r="O24" t="n">
-        <v>3.91</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>3.82</v>
+        <v>6.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.81</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>2.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.79</v>
+        <v>3.45</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O26" t="n">
-        <v>4.11</v>
+        <v>3.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.2</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.15</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.46</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.71</v>
+        <v>4.15</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N29" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,109 +742,109 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,26 +861,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
         <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
         <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="T6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
         <v>9.800000000000001</v>
@@ -1174,10 +1174,10 @@
         <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
         <v>3.08</v>
@@ -1186,22 +1186,22 @@
         <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD6" t="n">
         <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46055.39583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>4.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>7.35</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.32</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.72</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>6.5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.94</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>2.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.32</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.78</v>
+        <v>2.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="O18" t="n">
-        <v>2.24</v>
+        <v>4.78</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="T19" t="n">
         <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB19" t="n">
         <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46055.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="O21" t="n">
-        <v>2.55</v>
+        <v>3.91</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>5.85</v>
+        <v>3.82</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.86</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>1.68</v>
+        <v>5.02</v>
       </c>
       <c r="O22" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="T22" t="n">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.71</v>
+        <v>1.81</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>2.23</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.79</v>
+        <v>4.25</v>
       </c>
       <c r="M23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.68</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>5.02</v>
+        <v>2.64</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.79</v>
+        <v>3.82</v>
       </c>
       <c r="T24" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.28</v>
+        <v>5.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>2.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>3.79</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.82</v>
+        <v>2.21</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="U25" t="n">
         <v>1.68</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
         <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
         <v>1.09</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3.91</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.53</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="V26" t="n">
-        <v>3.82</v>
+        <v>5.85</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="M27" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>3.02</v>
+        <v>4.46</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>2.93</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T27" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="V27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AC27" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,64 +3991,64 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O30" t="n">
         <v>4.5</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4.2</v>
-      </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="T30" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="U30" t="n">
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
         <v>1.8</v>
@@ -4057,7 +4057,7 @@
         <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46055.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.25</v>
       </c>
-      <c r="N31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.68</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O32" t="n">
         <v>2.5</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V32" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,32 +742,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T3" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,32 +861,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1237,90 +1237,90 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.54</v>
+        <v>6.64</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="O7" t="n">
-        <v>6.04</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="U7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46055.41666666666</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>5.38</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46055.44444444445</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>6.16</v>
+        <v>4.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
         <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.03</v>
+        <v>6.99</v>
       </c>
       <c r="R9" t="n">
         <v>1.49</v>
@@ -1522,7 +1522,7 @@
         <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1531,31 +1531,31 @@
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.54</v>
       </c>
-      <c r="AC9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="AH9" t="n">
         <v>2.13</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46055.51041666666</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46055.52083333334</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.05</v>
+        <v>4.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.84</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
         <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
@@ -1891,31 +1891,31 @@
         <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AF12" t="n">
         <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46055.54166666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.72</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>7.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.75</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>10.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.04</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>5.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
         <v>6.25</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.25</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
         <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.65</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18</v>
+        <v>2.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.699999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.55</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
         <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.32</v>
+        <v>4.51</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.36</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z19" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46055.625</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.76</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.91</v>
+        <v>2.14</v>
       </c>
       <c r="P21" t="n">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>6.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>3.82</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.2</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>5.02</v>
+        <v>2.64</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.79</v>
+        <v>3.82</v>
       </c>
       <c r="T22" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.28</v>
+        <v>5.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.93</v>
+        <v>1.39</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.81</v>
+        <v>2.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="O23" t="n">
-        <v>4.42</v>
+        <v>3.91</v>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V23" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="AG23" t="n">
         <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>4.4</v>
+        <v>5.85</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.35</v>
+        <v>3.86</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2.12</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>5.85</v>
+        <v>4.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.86</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.24</v>
+        <v>2.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4.46</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.93</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="T27" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="U27" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
         <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
         <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T28" t="n">
         <v>3.05</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.23</v>
-      </c>
       <c r="U28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V28" t="n">
+        <v>9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M29" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>4.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.46</v>
+        <v>2.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="T29" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="V29" t="n">
         <v>10</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="M31" t="n">
         <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
         <v>3.25</v>
@@ -4125,25 +4125,25 @@
         <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R31" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U31" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
         <v>1.08</v>
@@ -4152,16 +4152,16 @@
         <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD31" t="n">
         <v>1.22</v>
@@ -4170,13 +4170,13 @@
         <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
         <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="P32" t="n">
         <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.68</v>
+        <v>5.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W32" t="n">
         <v>1.06</v>
@@ -4268,25 +4268,25 @@
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA32" t="n">
         <v>2.26</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
         <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
         <v>1.75</v>
@@ -4295,7 +4295,7 @@
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4467,37 +4467,37 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>4.94</v>
       </c>
       <c r="R34" t="n">
         <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T34" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="U34" t="n">
         <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
@@ -4509,16 +4509,16 @@
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD34" t="n">
         <v>1.22</v>
@@ -4530,10 +4530,10 @@
         <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46055.75</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,32 +742,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,32 +861,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1597,17 +1597,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1964,77 +1964,77 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
         <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46055.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>7.75</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="P14" t="n">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.9</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.18</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Z14" t="n">
         <v>4.3</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.75</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.25</v>
+        <v>1.12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>8.27</v>
       </c>
       <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.67</v>
       </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.6</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>2.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>5.25</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.94</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2801,67 +2801,67 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O20" t="n">
-        <v>8.08</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
         <v>1.2</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>4.49</v>
       </c>
       <c r="O21" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.18</v>
+        <v>5.63</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.64</v>
+        <v>3.42</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
         <v>4.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.2</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>5.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="O24" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="V24" t="n">
-        <v>5.85</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.2</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="M26" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
         <v>4.42</v>
       </c>
       <c r="P26" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.12</v>
       </c>
-      <c r="R26" t="n">
+      <c r="AD26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.22</v>
       </c>
-      <c r="S26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3637,49 +3637,49 @@
         <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
       <c r="T27" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
         <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
         <v>1.53</v>
@@ -3688,19 +3688,19 @@
         <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46055.6875</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N28" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T28" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="U28" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46055.6875</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>4.46</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S29" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46055.6875</v>
@@ -3991,70 +3991,70 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>4.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
         <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S30" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="T30" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="V30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH30" t="n">
         <v>1.22</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
         <v>3.25</v>
@@ -4134,43 +4134,43 @@
         <v>2.45</v>
       </c>
       <c r="T31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
         <v>1.36</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="M32" t="n">
         <v>3.55</v>
@@ -4241,61 +4241,61 @@
         <v>2.41</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.55</v>
+        <v>5.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T32" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U32" t="n">
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46055.70833333334</v>
@@ -4348,37 +4348,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="N33" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="O33" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
         <v>1.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="T33" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V33" t="n">
-        <v>6.1</v>
+        <v>6.35</v>
       </c>
       <c r="W33" t="n">
         <v>1.06</v>
@@ -4387,34 +4387,34 @@
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46055.73958333334</v>
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="M36" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.99</v>
+        <v>4.33</v>
       </c>
       <c r="R36" t="n">
         <v>1.39</v>
@@ -4729,49 +4729,49 @@
         <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
         <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46055.89583333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,32 +742,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T3" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,32 +861,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,19 +2061,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>8.27</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>5.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,99 +2180,99 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.12</v>
       </c>
-      <c r="M15" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>11</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AH15" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2311,17 +2311,17 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>4.51</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.92</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.51</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2787,17 +2787,17 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,19 +2894,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.57</v>
+        <v>3.78</v>
       </c>
       <c r="M21" t="n">
-        <v>3.36</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>4.49</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.29</v>
+        <v>4.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.63</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>3.68</v>
       </c>
       <c r="T21" t="n">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.13</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.69</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.42</v>
+        <v>2.12</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3022,20 +3022,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3132,99 +3132,99 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.63</v>
+        <v>5.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="S23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB23" t="n">
         <v>3.1</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3251,99 +3251,99 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>5.05</v>
+        <v>3.63</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z24" t="n">
         <v>4.2</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7</v>
-      </c>
       <c r="AA24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,99 +3370,99 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>4.49</v>
       </c>
       <c r="O25" t="n">
-        <v>4.19</v>
+        <v>2.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="R25" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>2.73</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="U25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.93</v>
       </c>
-      <c r="V25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.24</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.97</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,99 +3489,99 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
-        <v>4.42</v>
+        <v>4.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AG26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3640,7 +3640,7 @@
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>2.75</v>
@@ -3652,43 +3652,43 @@
         <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S27" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE27" t="n">
         <v>1.95</v>
@@ -3739,24 +3739,24 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>3.2</v>
       </c>
       <c r="M28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
         <v>2.1</v>
@@ -3768,13 +3768,13 @@
         <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S28" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T28" t="n">
         <v>3.58</v>
@@ -3798,7 +3798,7 @@
         <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB28" t="n">
         <v>1.4</v>
@@ -3855,20 +3855,20 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -4093,20 +4093,20 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4467,67 +4467,67 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.94</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V34" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="W34" t="n">
         <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="AA34" t="n">
         <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC34" t="n">
         <v>3.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
         <v>1.3</v>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.79</v>
       </c>
       <c r="N35" t="n">
         <v>3.8</v>
@@ -4705,16 +4705,16 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="O36" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P36" t="n">
         <v>2.15</v>
@@ -4723,16 +4723,16 @@
         <v>4.33</v>
       </c>
       <c r="R36" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
         <v>7</v>
@@ -4741,22 +4741,22 @@
         <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD36" t="n">
         <v>1.25</v>
@@ -4771,7 +4771,7 @@
         <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46055.89583333334</v>

--- a/jogos_2026-02-02.xlsx
+++ b/jogos_2026-02-02.xlsx
@@ -742,32 +742,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>4.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S3" t="n">
-        <v>3.84</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>3.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.07</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.95</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46055.35416666666</v>
@@ -861,32 +861,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.5</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.84</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>5.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.48</v>
+        <v>2.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46055.35416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.12</v>
+        <v>5.25</v>
       </c>
       <c r="M14" t="n">
-        <v>8.27</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.85</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>4.33</v>
+        <v>6.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.52</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.8</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>8.27</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.3</v>
+        <v>5.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="AG16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46055.58333333334</v>
@@ -2418,22 +2418,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.51</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2537,22 +2537,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>4.51</v>
       </c>
       <c r="M18" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.92</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46055.60416666666</v>
@@ -2894,22 +2894,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>4.42</v>
+        <v>4.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3013,22 +3013,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>3.63</v>
       </c>
       <c r="N22" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>4.65</v>
+        <v>5.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3132,99 +3132,99 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>5.05</v>
+        <v>3.96</v>
       </c>
       <c r="N23" t="n">
-        <v>1.66</v>
+        <v>3.42</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.14</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE23" t="n">
         <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,16 +3251,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>3.63</v>
+        <v>3.36</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>4.49</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="P24" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>5.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.2</v>
+        <v>3.13</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3385,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>3.78</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>4.49</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>2.29</v>
+        <v>4.42</v>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.63</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="S25" t="n">
-        <v>2.73</v>
+        <v>3.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.13</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.69</v>
+        <v>2.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.42</v>
+        <v>2.12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46055.66666666666</v>
@@ -3489,22 +3489,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.71</v>
+        <v>3.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="AG26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46055.66666666666</v>
@@ -4212,20 +4212,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4331,20 +4331,20 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4453,17 +4453,17 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.79</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
         <v>3.8</v>
@@ -4708,13 +4708,13 @@
         <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="N36" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="O36" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="P36" t="n">
         <v>2.15</v>
@@ -4726,13 +4726,13 @@
         <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
         <v>2.88</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
         <v>7</v>
@@ -4747,16 +4747,16 @@
         <v>1.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD36" t="n">
         <v>1.25</v>
@@ -4771,7 +4771,7 @@
         <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46055.89583333334</v>
